--- a/output/pdf_financials_xlsx/IFC.xlsx
+++ b/output/pdf_financials_xlsx/IFC.xlsx
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-581</v>
+        <v>-568</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-942</v>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2297</v>
+        <v>2310</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>3365</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2297</v>
+        <v>2310</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>3365</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2878</v>
+        <v>3604</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4307</v>
+        <v>5104</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>20.18763029881862</v>
+        <v>19.7359277275886</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>21.87137218481542</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>2297</v>
+        <v>2310</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>3365</v>
@@ -2794,15 +2794,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>1171</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>997</v>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
@@ -2852,15 +2848,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>997</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>1213</v>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
@@ -4702,7 +4694,11 @@
           <t>Cash and cash equivalents, net of bank overdraft, beginning of year</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>1171</v>
       </c>
@@ -4760,7 +4756,11 @@
           <t>Cash and cash equivalents, net of bank overdraft, end of year 30 $</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>997</v>
       </c>
@@ -5413,11 +5413,7 @@
           <t>Shareholders</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" s="5" t="n">
         <v>2297</v>
       </c>
@@ -6326,7 +6322,11 @@
           <t>Depreciation of property and equipment1</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E117" s="5" t="n">
         <v>163</v>
       </c>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">

--- a/output/pdf_financials_xlsx/IFC.xlsx
+++ b/output/pdf_financials_xlsx/IFC.xlsx
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>29989</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>26845</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
@@ -4142,7 +4142,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>29989</v>
       </c>
